--- a/8.Problems for Revision.xlsx
+++ b/8.Problems for Revision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\samyak\learning\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1957A761-4734-4152-8B9F-FDA29E2312D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3611EFD1-F8DD-42B4-9C91-B1BFD450B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>No.</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/reverse-words-in-a-string-iii/</t>
+  </si>
+  <si>
+    <t>Determine Whether Matrix Can Be Obtained By Rotation</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/determine-whether-matrix-can-be-obtained-by-rotation/</t>
   </si>
 </sst>
 </file>
@@ -505,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="10.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -635,6 +641,23 @@
         <v>21</v>
       </c>
     </row>
+    <row r="8" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1886</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{EAC7D82D-1B54-4387-827E-D7BC20CD016A}"/>
@@ -647,8 +670,9 @@
     <hyperlink ref="D6" r:id="rId8" xr:uid="{ED55146A-CD7F-450F-B3CB-47C75F778453}"/>
     <hyperlink ref="E6" r:id="rId9" xr:uid="{AF5291B1-4AD5-4DD3-80E5-796A13474C60}"/>
     <hyperlink ref="D7" r:id="rId10" xr:uid="{D7802CF5-374A-4EA2-AB72-CFEA92A16B5B}"/>
+    <hyperlink ref="D8" r:id="rId11" xr:uid="{00C7E301-9B2F-4332-9400-AD57CCF8611E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
--- a/8.Problems for Revision.xlsx
+++ b/8.Problems for Revision.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\samyak\learning\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3611EFD1-F8DD-42B4-9C91-B1BFD450B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEB0758-CC51-40B1-96CB-1F2D7690145A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Revision" sheetId="1" r:id="rId1"/>
+    <sheet name="Two Pointers" sheetId="1" r:id="rId1"/>
+    <sheet name="Fast&amp;Slow Pointers" sheetId="3" r:id="rId2"/>
+    <sheet name="Sliding Window" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>No.</t>
   </si>
@@ -103,13 +105,52 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/determine-whether-matrix-can-be-obtained-by-rotation/</t>
+  </si>
+  <si>
+    <t>Linked List Cycle II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
+  </si>
+  <si>
+    <t>Find the Duplicate Number</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-the-duplicate-number/</t>
+  </si>
+  <si>
+    <t>Palindrome Linked List</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/palindrome-linked-list/</t>
+  </si>
+  <si>
+    <t>Day/90</t>
+  </si>
+  <si>
+    <t>Circular Array Loop</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/circular-array-loop/</t>
+  </si>
+  <si>
+    <t>Maximum Sum of Distinct Subarrays With Length K</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-sum-of-distinct-subarrays-with-length-k/</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-size-subarray-sum/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,29 +181,16 @@
     </font>
     <font>
       <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
       <sz val="13"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
     </font>
     <font>
       <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
     </font>
   </fonts>
   <fills count="3">
@@ -207,7 +235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -218,16 +246,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,14 +534,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="10.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="129.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="68.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.5546875" style="3"/>
+    <col min="3" max="3" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="129.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="129.5546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
@@ -539,7 +561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>410</v>
       </c>
@@ -552,11 +574,11 @@
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1365</v>
       </c>
@@ -569,11 +591,11 @@
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>246</v>
       </c>
@@ -586,7 +608,7 @@
       <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -603,11 +625,11 @@
       <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>151</v>
       </c>
@@ -620,7 +642,7 @@
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -637,11 +659,11 @@
       <c r="D7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1886</v>
       </c>
@@ -654,7 +676,7 @@
       <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -675,4 +697,177 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743C308A-D4BA-4432-93E6-9F820BE791E9}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="129.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="87.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="129.5546875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>142</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>287</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>234</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>457</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B6B865-EB38-4854-9FD2-CC18C3ADCFDB}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>209</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2461</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>